--- a/auction_xref/Auction - top 30 by discount.xlsx
+++ b/auction_xref/Auction - top 30 by discount.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Sept 169</t>
+          <t>361373</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -652,7 +652,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Still available - unsold, offers invited</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Sept 119</t>
+          <t>350867</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Still available - unsold, offers invited</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Sept 152</t>
+          <t>360855</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Still available - unsold, offers invited</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr"/>
@@ -1074,49 +1074,49 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>49 Exmouth Road, Great Yarmouth, Norfolk, NR30 3DP</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Sept 101</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>361410</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="12">
         <f>D14*1.1</f>
         <v>33000.0</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="12" t="n">
         <v>81000</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="13">
         <f>D14/F14</f>
         <v>0.3703703704</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="13">
         <f>1-G14</f>
         <v>0.6296296296</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr"/>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>Still available - unsold, offers invited</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1365,43 +1365,43 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>4 Milburn Street, Crook, County Durham, DL15 9DY</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Sept 166A</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n">
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>362208</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="12">
         <f>D21*1.1</f>
         <v>44000.0</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="12" t="n">
         <v>92500</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="13">
         <f>D21/F21</f>
         <v>0.4324324324</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="13">
         <f>1-G21</f>
         <v>0.5675675676</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Still available - unsold, offers invited</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1486,82 +1486,82 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Flat 3, 9 Queensland Road, Highbury, London, N7 7FH</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Sept 117</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>359566</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>145000</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="12">
         <f>D24*1.1</f>
         <v>159500.0</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="12" t="n">
         <v>297000</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="13">
         <f>D24/F24</f>
         <v>0.4882154882</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="13">
         <f>1-G24</f>
         <v>0.5117845118</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr"/>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>Still available - unsold, offers invited</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>29 Hervey Street, Lowestoft, Suffolk, NR32 2JG</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Sept 63</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="n">
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>361511</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="12">
         <f>D25*1.1</f>
         <v>82500.0</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="12" t="n">
         <v>153000</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="13">
         <f>D25/F25</f>
         <v>0.4901960784</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="13">
         <f>1-G25</f>
         <v>0.5098039216</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>Still available - unsold, offers invited</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1685,43 +1685,43 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>29A High Street, March, Cambridgeshire, PE15 0XA</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Sept 111</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n">
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>358027</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>95000</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="12">
         <f>D29*1.1</f>
         <v>104500.0</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="12" t="n">
         <v>178000</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="13">
         <f>D29/F29</f>
         <v>0.5337078652</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="13">
         <f>1-G29</f>
         <v>0.4662921348</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr"/>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>Still available - unsold, offers invited</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>Not in October catalogue - availability unconfirmed</t>
+          <t>Not listed - sold or withdrawn</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -1894,116 +1894,109 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>AVAILABILITY - READ BEFORE ACTING</t>
+          <t>Availability</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Only 3 of these 30 are confirmed in the 7-8 October catalogue (shaded green).</t>
+          <t>11 of these 30 can still be bought (shaded green): either in the 7-8 October</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>The rest come from our September tracked list. That auction has run, so they may have sold,</t>
+          <t>catalogue, or on the auction house's 'lots still available' list, where unsold lots from</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>been withdrawn, or remain unsold and available - we cannot tell from what we hold. Checking</t>
+          <t>past sales take offers directly. The rest appear on neither page, so they sold at the</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>needs the auction house's 'lots still available' page, which has not been captured.</t>
+          <t>September auction or were withdrawn - reference only, not actionable.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Only 11 of the 107 October lots have a Hometrack valuation at all, which is why a top 30</t>
+          <t>Both pages fetched from the site on 16 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>cannot be drawn from the October sale alone.</t>
-        </is>
-      </c>
+      <c r="A19" s="15" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr"/>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>VALUATION CHECK COLUMN</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>VALUATION CHECK COLUMN</t>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>14 of these 30 are shaded amber because the Hometrack figure is not cleanly for the</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>14 of these 30 are shaded amber because the Hometrack figure is not cleanly for the</t>
+          <t>lot being sold - it is the whole building, a representative unit, or a neighbouring property.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>lot being sold - it is the whole building, a representative unit, or a neighbouring property.</t>
+          <t>Their discounts may be fiction. The caveats come from the source spreadsheet's own notes.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Their discounts may be fiction. The caveats come from the source spreadsheet's own notes.</t>
+          <t>A very large discount on an amber row is a reason to check the valuation, not to bid.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>A very large discount on an amber row is a reason to check the valuation, not to bid.</t>
-        </is>
-      </c>
+      <c r="A25" s="15" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr"/>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>Sources</t>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Guides: auctionhouselondon.co.uk/current-auction, fetched 16 September 2026, for lots in the</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Guides: auctionhouselondon.co.uk/current-auction, fetched 16 September 2026, for lots in the</t>
+          <t>October sale; the September catalogue otherwise. Hometrack valuations: from the source</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>October sale; the September catalogue otherwise. Hometrack valuations: from the source</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>spreadsheet, Dropbox /Clients/Vance/110 portfolio/October auction.xlsx.</t>
         </is>
